--- a/artfynd/A 43388-2023 artfynd.xlsx
+++ b/artfynd/A 43388-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43388-2023 artfynd.xlsx
+++ b/artfynd/A 43388-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3058097</v>
+        <v>3058096</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>374684.5501946824</v>
+        <v>374685</v>
       </c>
       <c r="R2" t="n">
-        <v>6599207.16123017</v>
+        <v>6599207</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,29 +747,14 @@
           <t>Stavnäs</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>S-Arv-0315</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>2011-12-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-12-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,19 +784,15 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Värmland Floraväktarna</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elvi Eriksson, Per Larsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Per Larsson, Elvi Eriksson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
